--- a/outreach/NL and Stockholm Corporate Community Contacts.xlsx
+++ b/outreach/NL and Stockholm Corporate Community Contacts.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Stockholm" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Netherlands'!$A$1:$U$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stockholm'!$A$1:$U$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Netherlands'!$A$1:$V$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stockholm'!$A$1:$V$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -598,69 +598,83 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gmail drafts (2 Oct)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>43 of the 45 Tier A organisations have a draft ready in Brian’s Gmail (Gmail draft column, Status = Draft ready). Send or schedule them from the Gmail screen so the venue link stays a normal fcurban.com link. EDGE Olympic and Sickla Central were not drafted; the Next step column says why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Columns worth knowing</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Nearest live FC Urban venue: venues with weekday evening games in the next 14 days (checked 2 Oct). Walk time = straight line x 1.3 at 80 m per minute. Only claim "we already play near you" when it is 15 minutes or less.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Budget evidence: why we think they pay for events themselves (free tenant events, service charge, BIZ levy, paid community team). Blank means we found nothing, not that there is no budget.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Status: drop down, update it as you go (To do, Contacted, Replied, Call booked, Not interested).</t>
+          <t>Nearest live FC Urban venue: venues with weekday evening games in the next 14 days (checked 2 Oct). Walk time = straight line x 1.3 at 80 m per minute. Only claim "we already play near you" when it is 15 minutes or less.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Budget evidence: why we think they pay for events themselves (free tenant events, service charge, BIZ levy, paid community team). Blank means we found nothing, not that there is no budget.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Status: drop down, update it as you go (Draft ready, To do, Contacted, Sent, Replied, Call booked, Not interested).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Things to know</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Stockholm: only Råstasjöns IP (Solna) has live games right now, so almost every Stockholm message should say "we are opening new weekly games near you" rather than naming a venue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Brian's Gmail has no history with any of these domains. The 12 "Do not contact" rows come from the shared suppression list (mostly Stockholm coworking spaces, Fabege, Impact Hub and Norrsken).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Contacts and emails were only taken from the organisations' own sites, press or public search results. Nothing was guessed; check the Source column if in doubt.</t>
+          <t>Stockholm: only Råstasjöns IP (Solna) has live games right now, so almost every Stockholm message should say "we are opening new weekly games near you" rather than naming a venue.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Brian's Gmail has no history with any of these domains. The 12 "Do not contact" rows come from the shared suppression list (mostly Stockholm coworking spaces, Fabege, Impact Hub and Norrsken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Contacts and emails were only taken from the organisations' own sites, press or public search results. Nothing was guessed; check the Source column if in doubt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>English is fine for both countries; a Dutch or Swedish first line can help with smaller organisations.</t>
         </is>
@@ -677,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U103"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -695,12 +709,13 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,30 +796,35 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
+          <t>Gmail draft</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Next step</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -886,30 +906,35 @@
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
+          <t>r-6006123067746709560</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
           <t>+31 20 575 2000</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
           <t>https://www.wtcamsterdam.com/service-team</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>Tenant app plus ambassador club of tenant office managers; community team members named across sources: Rik Kooi, Bente, Jeanine, Annemarie Engels, Eva Diks (check who is current). Same Socialclub concept as WTC Utrecht, Delftse Poort, WTC Schiphol. No bedrijvenvoetbal found yet, so a weekly after work football game would be new.</t>
         </is>
@@ -991,30 +1016,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
+          <t>r1168534885441049520</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)20 333 7441</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
           <t>https://en.hellozuidas.com/contact</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>Other team: Angela Ham (Service Point), Rinske Berg and Elisa Schouten (project managers). Hello Zuidas app lists corporate sports organisers (Corporate Sports Events) as local partners, so a football league would fit the existing ecosystem. Magazine contact: info@zuidaspublishers.nl. | also: servicepoint@hellozuidas.com; https://www.wtcamsterdam.com/en/facilities/hello-zuidas/</t>
         </is>
@@ -1096,30 +1126,35 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
+          <t>r-3962955930959591703</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
           <t>010 303 8288</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
           <t>https://delftsepoort.nl/en/our-community/socialclub/</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Community app with groups for shared interests (cycling, chess). Located in the Rotterdam Central District (Weena). Lieke's mobile 06-50075119 appears in a search snippet only.</t>
         </is>
@@ -1201,30 +1236,35 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
+          <t>r8567461906721126186</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)88 336 36 36</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
           <t>https://www.papendorp.nl/nl/organisatie</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>Chair Laurens Kroeze; operations led by Bas Kemper (SWECO). Corporate runs show appetite for sports; KPMG, Deloitte, Broadcom on site. | also: welkom@papendorp.nl; https://www.papendorp.nl/nl/organisatie</t>
         </is>
@@ -1306,30 +1346,35 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
+          <t>r-4549097315443484538</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
           <t>06 222 42 177 (Rob Ittmann, from search snippet)</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
           <t>https://rotterdam-centraldistrict.nl/en/team/</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>Area manager Marjolein Smits van Oyen; chair Dominique van Elsacker. Board includes Unilever, a.s.r. real estate, CIC and the City of Rotterdam. Ideal umbrella for an inter-company league in central Rotterdam.</t>
         </is>
@@ -1401,28 +1446,33 @@
           <t>info@ondernemer-s.nl</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>r-6077854693472860860</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
           <t>https://www.ondernemer-s.nl/</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>No sport events found, only networking. Strijp-S general inbox info@park-strijp.nl (strijp-s.nl/contact). BIZ status not confirmed.</t>
         </is>
@@ -1504,30 +1554,35 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
+          <t>r-8651720054855014977</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
           <t>+31 30 3078200</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
           <t>https://www.wtcutrecht.nl/socialclub/</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>Next to Utrecht Central Station. Also hosts Green Business Club Utrecht. Another source names Jeanine as community manager; the Socialclub page names Anne-Marie Burger.</t>
         </is>
@@ -1609,30 +1664,35 @@
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
+          <t>r942754394560481485</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)20 316 3034</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
           <t>https://www.wtcschiphol.nl/socialclub/</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>Also linked to the Spot Schiphol Community for the wider 65,000-person Schiphol workforce.</t>
         </is>
@@ -1714,30 +1774,35 @@
       </c>
       <c r="P10" s="5" t="inlineStr">
         <is>
+          <t>r7670566007120918937</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
           <t>+31 50 361 01 41</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
           <t>https://campusgroningen.nl/en/about-us/team</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>Kelly Kroeze handles content, creative and events. Director Edward van der Meer, edward@campusgroningen.nl, 050 361 50 50. No sports found yet.</t>
         </is>
@@ -1819,30 +1884,35 @@
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
+          <t>r3154456108834178407</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)71 524 75 55</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
           <t>https://leidenbiosciencepark.nl/contact/</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Already runs an inter-company football league, so this is a competitor-incumbent or partnership case. Sports contact at the University Sports Centre: Sebastian Schoenmaker, s.d.schoenmaker@usc.leidenuniv.nl. Also listed: Annemarie Spigt (Junior Marketing and Events), Liesbeth Eggink (Director Operations &amp; Business Development).</t>
         </is>
@@ -1916,30 +1986,35 @@
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
+          <t>r1411855039706768920</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)6 12448821</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
           <t>https://businessclubnv.nl/sports/</t>
         </is>
       </c>
-      <c r="U12" s="5" t="inlineStr">
+      <c r="V12" s="5" t="inlineStr">
         <is>
           <t>Small rural entrepreneurs club with a sports programme; a football add-on is plausible.</t>
         </is>
@@ -2013,30 +2088,35 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
+          <t>r3739249648654621724</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
           <t>085 212 9178</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
           <t>https://nestcowork.nl/community/</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>Small but very active social calendar. No named community manager.</t>
         </is>
@@ -2118,30 +2198,35 @@
       </c>
       <c r="P14" s="5" t="inlineStr">
         <is>
+          <t>r2852026013049801229</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
           <t>+31 88 999 57 00</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
           <t>https://www.brightlands.com/en/chemelot-campus/brightlands-chemelot-campus-community</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>Email shown on site as sigrid.paans [at] brightlands.com. Search results also list Karin Meulenberg (Manager Community Events), Maud Simons (Event officer). Vitality inbox brightlands@markspt.nl. Brightlands Sportinnovator Center on campus.</t>
         </is>
@@ -2221,28 +2306,33 @@
           <t>info@park-strijp.nl</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>r2195429627340704418</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
           <t>https://riumssen.nl/blog/case/office-s/</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>info@park-strijp.nl is the general Strijp-S address. A tournament (KUBBS) already runs, good sign for a football league.</t>
         </is>
@@ -2320,30 +2410,35 @@
       </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
+          <t>r-8008141214474039853</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
           <t>+31 20 2612 100</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
           <t>https://www.volkshotel.nl/en/blog/art-cult/space-to-work-and-create</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>Creative studio community, not corporate; also a free public coworking space in the lobby. Source article may be dated, so confirm Hilde van Wijk is still in post.</t>
         </is>
@@ -2421,30 +2516,35 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
+          <t>r-5537512300321375568</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
           <t>+31 20 811 2811</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
           <t>https://livezoku.com/amsterdam/cowork/</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="V17" s="5" t="inlineStr">
         <is>
           <t>Hotel plus coworking; private WhatsApp group for members. Hotel guests and residents also use the space.</t>
         </is>
@@ -2512,32 +2612,33 @@
           <t>sales@edgeworkspaces.com</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>+31 20 218 3311</t>
         </is>
       </c>
-      <c r="Q18" s="5" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
+          <t>Not drafted: only a sales@ inbox is published. Find the community manager on LinkedIn instead.</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>https://www.edgeworkspaces.com/locations/amsterdam/olympic/</t>
         </is>
       </c>
-      <c r="U18" s="5" t="inlineStr">
+      <c r="V18" s="5" t="inlineStr">
         <is>
           <t>WELL Platinum building with smart building app (bGrid). Only a sales inbox published.</t>
         </is>
@@ -2605,28 +2706,33 @@
           <t>events@fosbury.amsterdam</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>r2234174149901403613</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
           <t>https://www.fosburyamsterdam.com/contact</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>Events inbox published on the contact page (events@); general inbox prinsengracht@fosbury.amsterdam and memberships enjoy@fosbury.amsterdam. Former Prinsengracht hospital; members-only events. No staff names published.</t>
         </is>
@@ -2704,30 +2810,35 @@
       </c>
       <c r="P20" s="5" t="inlineStr">
         <is>
+          <t>r6423891320934656625</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
           <t>+31 20 261 4703</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
           <t>https://b-amsterdam.com/en/work/cowork/</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="V20" s="5" t="inlineStr">
         <is>
           <t>Name and cowork@ email come from a public search result of the B. cowork pages; the page itself also lists rent@b-amsterdam.com and Jasmijn as tour contact. 12 indoor padel courts, gym and golf simulator on site; already runs its own Business Run. Strong fit for a football league. Who pays for events not stated.</t>
         </is>
@@ -2801,30 +2912,35 @@
       </c>
       <c r="P21" s="5" t="inlineStr">
         <is>
+          <t>r3420887048009108444</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)20 622 21 11</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
           <t>https://www.oram.nl/</t>
         </is>
       </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>Regional business network rather than one district. Sport is not a main focus in the evidence found. KvK 34169371. Good partner for reaching Amsterdam employers.</t>
         </is>
@@ -2906,30 +3022,35 @@
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
+          <t>r-1091190216872107734</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
           <t>+31 6 10 73 10 43</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
           <t>https://www.kadans.com/science-clusters/rotterdam-science-cluster-rotterdam/</t>
         </is>
       </c>
-      <c r="U22" s="5" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>Life-science / lab tower with auditorium and restaurant. General inbox info@kadans.com, +31 88 0500 777.</t>
         </is>
@@ -3011,30 +3132,35 @@
       </c>
       <c r="P23" s="5" t="inlineStr">
         <is>
+          <t>r-1975412592311372877</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
           <t>+31 20 8208060</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
           <t>https://www.amsterdamsciencepark.nl/contact/amsterdam-science-park-business-club/</t>
         </is>
       </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="V23" s="5" t="inlineStr">
         <is>
           <t>Details come from a search result because the site returned 503 / 404. Business Club inbox is events@; director also has Scienceandbusiness@amsterdamsciencepark.nl. Includes Startup Village and Matrix ONE. Strong fit for an inter-company league.</t>
         </is>
@@ -3116,30 +3242,35 @@
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
+          <t>r7808896599030602284</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)10 405 44 44</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
           <t>https://www.wtcrotterdam.com/en/about-wtc/tenants</t>
         </is>
       </c>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>Service desk: servicedesk@wtcrotterdam.com. No named community manager found; Postillion hotel in complex.</t>
         </is>
@@ -3217,30 +3348,35 @@
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
+          <t>r-8868766703719520940</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
           <t>+31 20 5321840</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T25" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
           <t>https://www.wearebeyond.work/beyond-republica-campus</t>
         </is>
       </c>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>Also beyond Gouden Bocht (Herengracht) and Zuidtoren (Hoofddorp). Workspace app for members.</t>
         </is>
@@ -3308,28 +3444,33 @@
           <t>info@brainportindustriescampus.com</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>r-1071650018843873423</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T26" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
           <t>https://www.brainportindustriescampus.com/en/contact/</t>
         </is>
       </c>
-      <c r="U26" s="5" t="inlineStr">
+      <c r="V26" s="5" t="inlineStr">
         <is>
           <t>Sports activities mentioned generically, no specifics found. Secretariaat inbox secretariaat@brainportindustriescampus.com per events page.</t>
         </is>
@@ -3407,30 +3548,35 @@
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
+          <t>r4667246944946825116</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
           <t>+31 30 800 4499</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
           <t>https://www.utrechtsciencepark.nl/</t>
         </is>
       </c>
-      <c r="U27" s="5" t="inlineStr">
+      <c r="V27" s="5" t="inlineStr">
         <is>
           <t>Vacancy page now 404 so the role may be filled; ask for the current events manager. Annemarie Dijkman (Project Manager, housing) is not the events contact.</t>
         </is>
@@ -3506,28 +3652,33 @@
           <t>wesley@basecamputrecht.nl</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>r-7589294780117109258</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
           <t>https://www.werkspoorkwartier.nl/ontdek-and-onderneem</t>
         </is>
       </c>
-      <c r="U28" s="5" t="inlineStr">
+      <c r="V28" s="5" t="inlineStr">
         <is>
           <t>Tenant community app is a good channel for announcing a league. No named community manager on the campus site.</t>
         </is>
@@ -3605,30 +3756,35 @@
       </c>
       <c r="P29" s="5" t="inlineStr">
         <is>
+          <t>r-1768265311623729269</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)70 304 53 00</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
           <t>https://www.wtcthehague.com/en/contact/team</t>
         </is>
       </c>
-      <c r="U29" s="5" t="inlineStr">
+      <c r="V29" s="5" t="inlineStr">
         <is>
           <t>Managing Director Eveline Kolk (offices@wtcthehague.com). No Socialclub-style sports programme found. Njoy Fitness on the ground floor.</t>
         </is>
@@ -3700,28 +3856,33 @@
           <t>tudelftcampus@tudelft.nl</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>r-2636131040111248988</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
           <t>https://www.tudelftcampus.nl/events</t>
         </is>
       </c>
-      <c r="U30" s="5" t="inlineStr">
+      <c r="V30" s="5" t="inlineStr">
         <is>
           <t>Address and phone not on events page. YES!Delft is a separate row.</t>
         </is>
@@ -3791,30 +3952,35 @@
       </c>
       <c r="P31" s="5" t="inlineStr">
         <is>
+          <t>r-1679590162593415485</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
           <t>+31 40 23 05 500</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
           <t>https://www.hightechcampus.com/contact</t>
         </is>
       </c>
-      <c r="U31" s="5" t="inlineStr">
+      <c r="V31" s="5" t="inlineStr">
         <is>
           <t>Football tournament page (2024) now 404; sports sections are community-initiated. Only named contact is Hilde de Vocht (media and press), not the events team. Ask for the community / campus sports team via info@.</t>
         </is>
@@ -3892,30 +4058,35 @@
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
+          <t>r3252161940687203843</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
           <t>020 20 666 40</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="inlineStr">
+      <c r="R32" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
           <t>https://www.schipholtradeparkservices.nl/businessclub/businessclub/</t>
         </is>
       </c>
-      <c r="U32" s="5" t="inlineStr">
+      <c r="V32" s="5" t="inlineStr">
         <is>
           <t>Area manager acts as secretary of the Businessclub (board of five elected by users). Sports facilities on site at New Terra hub.</t>
         </is>
@@ -3989,30 +4160,35 @@
       </c>
       <c r="P33" s="5" t="inlineStr">
         <is>
+          <t>r-6429129810174814618</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
           <t>+31 (0)23 525 7826</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S33" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
           <t>https://www.waarderpolder.nl/lets-connect/</t>
         </is>
       </c>
-      <c r="U33" s="5" t="inlineStr">
+      <c r="V33" s="5" t="inlineStr">
         <is>
           <t>Also home to Launchpad023 and De Plek coworking. Industriekring Haarlem serves entrepreneurs in the same area.</t>
         </is>
@@ -4086,30 +4262,35 @@
       </c>
       <c r="P34" s="5" t="inlineStr">
         <is>
+          <t>r1808951766986065439</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
           <t>06 1877 1902</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="R34" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T34" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
           <t>https://ondernemendhoofddorp.nl/</t>
         </is>
       </c>
-      <c r="U34" s="5" t="inlineStr">
+      <c r="V34" s="5" t="inlineStr">
         <is>
           <t>Chair Dick Hulsebosch according to a news article. Beukenhorst has a separate 'Beukenhorst Bruist' entrepreneur event (Rabobank Regio Schiphol, Vastgoed Haarlemmermeer, municipality).</t>
         </is>
@@ -4191,30 +4372,35 @@
       </c>
       <c r="P35" s="5" t="inlineStr">
         <is>
+          <t>r-2414322620143382358</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
           <t>+31 317 480 100</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S35" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
           <t>https://www.wageningencampus.nl/en/campus/contact-1/wageningen-campus-team.htm</t>
         </is>
       </c>
-      <c r="U35" s="5" t="inlineStr">
+      <c r="V35" s="5" t="inlineStr">
         <is>
           <t>Events: Flora de Ruiter. Manager: Anne Mensink (Manager Wageningen Campus &amp; Shared Facilities). The 230+ count is from a search snippet.</t>
         </is>
@@ -4296,30 +4482,35 @@
       </c>
       <c r="P36" s="5" t="inlineStr">
         <is>
+          <t>r2039920189136666130</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
           <t>+31 71 20 20 307</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
           <t>https://www.sbicnoordwijk.nl/job-vacancy-event-coordinator-sbic-nlspacecampus/</t>
         </is>
       </c>
-      <c r="U36" s="5" t="inlineStr">
+      <c r="V36" s="5" t="inlineStr">
         <is>
           <t>Vacancy dated 2024, role may be filled. Mainly start-up incubator community.</t>
         </is>
@@ -4389,30 +4580,35 @@
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
+          <t>r-2577099955742309828</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
           <t>020-820 44 59</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T37" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
           <t>https://www.pmsloterdijk.nl/</t>
         </is>
       </c>
-      <c r="U37" s="5" t="inlineStr">
+      <c r="V37" s="5" t="inlineStr">
         <is>
           <t>Business park under development. No sport events found; only networking meetings. Mailing address is the park manager's, not on site.</t>
         </is>
@@ -4484,28 +4680,33 @@
           <t>info@kennisparkondernemers.nl</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>r3366358724350558220</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
           <t>https://www.kennisparkondernemers.nl/</t>
         </is>
       </c>
-      <c r="U38" s="5" t="inlineStr">
+      <c r="V38" s="5" t="inlineStr">
         <is>
           <t>Board names on separate page. Address is the general campus address, not verified.</t>
         </is>
@@ -4569,32 +4770,33 @@
           <t>sales@edgeworkspaces.com</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>+31 20 218 3311</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R39" s="5" t="inlineStr">
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S39" s="5" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T39" s="5" t="inlineStr">
+      <c r="U39" s="5" t="inlineStr">
         <is>
           <t>https://www.edgeworkspaces.com/locations/amsterdam/stadium/</t>
         </is>
       </c>
-      <c r="U39" s="5" t="inlineStr">
+      <c r="V39" s="5" t="inlineStr">
         <is>
           <t>Near Olympic Stadium. EDGE Workspaces expanding to Rotterdam (Coolsingel) and Eindhoven in Q4 2026. Only a sales inbox published.</t>
         </is>
@@ -4666,32 +4868,33 @@
           <t>amsterdam.amstel@tribes.world</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>+31 20 238 10 00</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R40" s="5" t="inlineStr">
+      <c r="S40" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S40" s="5" t="inlineStr">
+      <c r="T40" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T40" s="5" t="inlineStr">
+      <c r="U40" s="5" t="inlineStr">
         <is>
           <t>https://www.tribes.world/locations/amsterdam-amstel-station</t>
         </is>
       </c>
-      <c r="U40" s="5" t="inlineStr">
+      <c r="V40" s="5" t="inlineStr">
         <is>
           <t>Name comes from a search result; events evidence is weak, so verify. Tribes team page also lists Otto Kaandorp as Community Manager (https://www.tribes.world/about-us/tribes-team). Tribes also has a South Axis (Zuidas) site.</t>
         </is>
@@ -4755,32 +4958,33 @@
           <t>reception@upofficebuilding.nl</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>+31 20 217 0999</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R41" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S41" s="5" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T41" s="5" t="inlineStr">
+      <c r="U41" s="5" t="inlineStr">
         <is>
           <t>https://upofficebuilding.nl/</t>
         </is>
       </c>
-      <c r="U41" s="5" t="inlineStr">
+      <c r="V41" s="5" t="inlineStr">
         <is>
           <t>Part of the CBRE Socialclub portfolio (with WTC Amsterdam, WTC Utrecht, Delftse Poort, NoMa House) per events.nl. Contact via reception for UP Social Club and events.</t>
         </is>
@@ -4844,32 +5048,33 @@
           <t>info@thehaguetech.com</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>070 206 0030</t>
         </is>
       </c>
-      <c r="Q42" s="5" t="inlineStr">
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R42" s="5" t="inlineStr">
+      <c r="S42" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S42" s="5" t="inlineStr">
+      <c r="T42" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr">
+      <c r="U42" s="5" t="inlineStr">
         <is>
           <t>https://thehaguetech.com</t>
         </is>
       </c>
-      <c r="U42" s="5" t="inlineStr">
+      <c r="V42" s="5" t="inlineStr">
         <is>
           <t>No named community manager on the homepage; check the team page.</t>
         </is>
@@ -4933,32 +5138,33 @@
           <t>success@nexpace.nl</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>+31 85 238 28 00</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="inlineStr">
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R43" s="5" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S43" s="5" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T43" s="5" t="inlineStr">
+      <c r="U43" s="5" t="inlineStr">
         <is>
           <t>https://nexpace.nl/en</t>
         </is>
       </c>
-      <c r="U43" s="5" t="inlineStr">
+      <c r="V43" s="5" t="inlineStr">
         <is>
           <t>Group-level contact (success@) from the homepage. Address not confirmed. Zuidoost business district, near Johan Cruijff Arena.</t>
         </is>
@@ -5022,32 +5228,33 @@
           <t>events@startdock.nl</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>+31 85 130 8310</t>
         </is>
       </c>
-      <c r="Q44" s="5" t="inlineStr">
+      <c r="R44" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R44" s="5" t="inlineStr">
+      <c r="S44" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S44" s="5" t="inlineStr">
+      <c r="T44" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T44" s="5" t="inlineStr">
+      <c r="U44" s="5" t="inlineStr">
         <is>
           <t>https://startdock.nl/en/contact</t>
         </is>
       </c>
-      <c r="U44" s="5" t="inlineStr">
+      <c r="V44" s="5" t="inlineStr">
         <is>
           <t>Published inboxes: info@startdock.nl, rent@startdock.nl (coworking and offices), events@startdock.nl (meeting rooms and events). Certified B Corp.</t>
         </is>
@@ -5115,32 +5322,33 @@
           <t>events@startdock.nl</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>+31 85 130 8310</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R45" s="5" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S45" s="5" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T45" s="5" t="inlineStr">
+      <c r="U45" s="5" t="inlineStr">
         <is>
           <t>https://startdock.nl/en/contact</t>
         </is>
       </c>
-      <c r="U45" s="5" t="inlineStr">
+      <c r="V45" s="5" t="inlineStr">
         <is>
           <t>events@ is the meeting rooms and events inbox; also rent@startdock.nl and info@startdock.nl. Certified B Corp, members include GetYourGuide. Good multi-site target.</t>
         </is>
@@ -5213,27 +5421,28 @@
         </is>
       </c>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R46" s="5" t="inlineStr">
+      <c r="S46" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S46" s="5" t="inlineStr">
+      <c r="T46" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T46" s="5" t="inlineStr">
+      <c r="U46" s="5" t="inlineStr">
         <is>
           <t>https://www.a-lab.nl</t>
         </is>
       </c>
-      <c r="U46" s="5" t="inlineStr">
+      <c r="V46" s="5" t="inlineStr">
         <is>
           <t>Community manager name from a search result of the A Lab team; the site also had a 2026 community manager vacancy (page now 404), so the person may have changed. Also event/production employee Sophie Verdonk. Former Shell lab in Amsterdam Noord, creative and cultural tenants.</t>
         </is>
@@ -5297,32 +5506,33 @@
           <t>hello@42workspace.com</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>010 333 0401</t>
         </is>
       </c>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R47" s="5" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S47" s="5" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T47" s="5" t="inlineStr">
+      <c r="U47" s="5" t="inlineStr">
         <is>
           <t>https://42workspace.com/</t>
         </is>
       </c>
-      <c r="U47" s="5" t="inlineStr">
+      <c r="V47" s="5" t="inlineStr">
         <is>
           <t>Has a fully equipped gym on site; rated 4.7/5 on Google per its site. A search snippet mentions Friday drinks and a daily buffet.</t>
         </is>
@@ -5394,32 +5604,33 @@
           <t>welcome@matrixic.nl</t>
         </is>
       </c>
-      <c r="P48" s="5" t="inlineStr">
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>+31 20 888 4500</t>
         </is>
       </c>
-      <c r="Q48" s="5" t="inlineStr">
+      <c r="R48" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R48" s="5" t="inlineStr">
+      <c r="S48" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S48" s="5" t="inlineStr">
+      <c r="T48" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T48" s="5" t="inlineStr">
+      <c r="U48" s="5" t="inlineStr">
         <is>
           <t>https://www.matrixic.nl/en/community/</t>
         </is>
       </c>
-      <c r="U48" s="5" t="inlineStr">
+      <c r="V48" s="5" t="inlineStr">
         <is>
           <t>Contact details from search result for Matrix Innovation Center; Margo Keizer from an amsterdamsciencepark.nl article (page returned 503 when fetched). Verify role.</t>
         </is>
@@ -5483,32 +5694,33 @@
           <t>info@ghg.nl</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>010 240 3434</t>
         </is>
       </c>
-      <c r="Q49" s="5" t="inlineStr">
+      <c r="R49" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R49" s="5" t="inlineStr">
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S49" s="5" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T49" s="5" t="inlineStr">
+      <c r="U49" s="5" t="inlineStr">
         <is>
           <t>https://ghg.nl</t>
         </is>
       </c>
-      <c r="U49" s="5" t="inlineStr">
+      <c r="V49" s="5" t="inlineStr">
         <is>
           <t>Leasing inbox leasing@ghg.nl. No named community manager found. Next to Rotterdam Central Station, inside the RCD area.</t>
         </is>
@@ -5580,32 +5792,33 @@
           <t>hello@startupvillage.nl</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr">
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>+31 85 273 31 27</t>
         </is>
       </c>
-      <c r="Q50" s="5" t="inlineStr">
+      <c r="R50" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R50" s="5" t="inlineStr">
+      <c r="S50" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S50" s="5" t="inlineStr">
+      <c r="T50" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T50" s="5" t="inlineStr">
+      <c r="U50" s="5" t="inlineStr">
         <is>
           <t>https://startupvillage.nl</t>
         </is>
       </c>
-      <c r="U50" s="5" t="inlineStr">
+      <c r="V50" s="5" t="inlineStr">
         <is>
           <t>Patricia Leek named on Amsterdam Science Park pages (search result). Email and phone from the Startup Village site. Sits on Amsterdam Science Park, so pair with the Science Park Business Club row.</t>
         </is>
@@ -5678,27 +5891,28 @@
         </is>
       </c>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R51" s="5" t="inlineStr">
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S51" s="5" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T51" s="5" t="inlineStr">
+      <c r="U51" s="5" t="inlineStr">
         <is>
           <t>https://www.impactcity.nl/en/apollo-14/</t>
         </is>
       </c>
-      <c r="U51" s="5" t="inlineStr">
+      <c r="V51" s="5" t="inlineStr">
         <is>
           <t>A search result named Dick Aerts as Community Manager of Apollo 14, not confirmed on the official page. Binckhaven area.</t>
         </is>
@@ -5762,32 +5976,33 @@
           <t>info@strijpcs.nl</t>
         </is>
       </c>
-      <c r="P52" s="5" t="inlineStr">
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>+31 6 1319 7466</t>
         </is>
       </c>
-      <c r="Q52" s="5" t="inlineStr">
+      <c r="R52" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R52" s="5" t="inlineStr">
+      <c r="S52" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S52" s="5" t="inlineStr">
+      <c r="T52" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T52" s="5" t="inlineStr">
+      <c r="U52" s="5" t="inlineStr">
         <is>
           <t>https://www.strijpcs.nl/en/our-community/</t>
         </is>
       </c>
-      <c r="U52" s="5" t="inlineStr">
+      <c r="V52" s="5" t="inlineStr">
         <is>
           <t>Non-profit, on Strijp-S; has foosball and table tennis. Events are mainly member-organised.</t>
         </is>
@@ -5852,27 +6067,28 @@
         </is>
       </c>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R53" s="5" t="inlineStr">
+      <c r="S53" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S53" s="5" t="inlineStr">
+      <c r="T53" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T53" s="5" t="inlineStr">
+      <c r="U53" s="5" t="inlineStr">
         <is>
           <t>https://ro-co.nl/</t>
         </is>
       </c>
-      <c r="U53" s="5" t="inlineStr">
+      <c r="V53" s="5" t="inlineStr">
         <is>
           <t>Small community, founded 2009. No named community manager on the site.</t>
         </is>
@@ -5936,32 +6152,33 @@
           <t>info@startdock.nl</t>
         </is>
       </c>
-      <c r="P54" s="5" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>+31 85 130 8310</t>
         </is>
       </c>
-      <c r="Q54" s="5" t="inlineStr">
+      <c r="R54" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R54" s="5" t="inlineStr">
+      <c r="S54" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S54" s="5" t="inlineStr">
+      <c r="T54" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T54" s="5" t="inlineStr">
+      <c r="U54" s="5" t="inlineStr">
         <is>
           <t>https://startdock.nl/en/contact</t>
         </is>
       </c>
-      <c r="U54" s="5" t="inlineStr">
+      <c r="V54" s="5" t="inlineStr">
         <is>
           <t>Same operator as the Rotterdam site; a single group-level conversation could cover both.</t>
         </is>
@@ -6025,32 +6242,33 @@
           <t>aandegracht@socialimpactfactory.com</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>030 227 3690</t>
         </is>
       </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="R55" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R55" s="5" t="inlineStr">
+      <c r="S55" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S55" s="5" t="inlineStr">
+      <c r="T55" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T55" s="5" t="inlineStr">
+      <c r="U55" s="5" t="inlineStr">
         <is>
           <t>https://www.socialimpactfactory.com/locaties/</t>
         </is>
       </c>
-      <c r="U55" s="5" t="inlineStr">
+      <c r="V55" s="5" t="inlineStr">
         <is>
           <t>Historic building next to the Dom. General inbox hallo@socialimpactfactory.com.</t>
         </is>
@@ -6114,32 +6332,33 @@
           <t>vredenburg@socialimpactfactory.com</t>
         </is>
       </c>
-      <c r="P56" s="5" t="inlineStr">
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>030 227 1812</t>
         </is>
       </c>
-      <c r="Q56" s="5" t="inlineStr">
+      <c r="R56" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R56" s="5" t="inlineStr">
+      <c r="S56" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S56" s="5" t="inlineStr">
+      <c r="T56" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T56" s="5" t="inlineStr">
+      <c r="U56" s="5" t="inlineStr">
         <is>
           <t>https://www.socialimpactfactory.com/locaties/</t>
         </is>
       </c>
-      <c r="U56" s="5" t="inlineStr">
+      <c r="V56" s="5" t="inlineStr">
         <is>
           <t>Certified B Corp, listed monument building. General inbox hallo@socialimpactfactory.com. 13 meeting rooms and a large event space.</t>
         </is>
@@ -6208,27 +6427,28 @@
         </is>
       </c>
       <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R57" s="5" t="inlineStr">
+      <c r="S57" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S57" s="5" t="inlineStr">
+      <c r="T57" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T57" s="5" t="inlineStr">
+      <c r="U57" s="5" t="inlineStr">
         <is>
           <t>https://www.werkspoorkwartier.nl/ontdek-and-onderneem</t>
         </is>
       </c>
-      <c r="U57" s="5" t="inlineStr">
+      <c r="V57" s="5" t="inlineStr">
         <is>
           <t>Contact email belongs to Werkspoorkathedraal, one building in the area. Already has a run event.</t>
         </is>
@@ -6301,27 +6521,28 @@
         </is>
       </c>
       <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr">
+      <c r="Q58" s="5" t="inlineStr"/>
+      <c r="R58" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R58" s="5" t="inlineStr">
+      <c r="S58" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S58" s="5" t="inlineStr">
+      <c r="T58" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T58" s="5" t="inlineStr">
+      <c r="U58" s="5" t="inlineStr">
         <is>
           <t>https://yesdelft.com/about/</t>
         </is>
       </c>
-      <c r="U58" s="5" t="inlineStr">
+      <c r="V58" s="5" t="inlineStr">
         <is>
           <t>Deeptech incubator partnered with TU Delft, Municipality of Delft and Erasmus University.</t>
         </is>
@@ -6393,32 +6614,33 @@
           <t>i.wouda@automotivecampus.com</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>+31 6 23111195</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="R59" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R59" s="5" t="inlineStr">
+      <c r="S59" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S59" s="5" t="inlineStr">
+      <c r="T59" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T59" s="5" t="inlineStr">
+      <c r="U59" s="5" t="inlineStr">
         <is>
           <t>https://www.automotivecampus.com/en/about-the-campus/about-us</t>
         </is>
       </c>
-      <c r="U59" s="5" t="inlineStr">
+      <c r="V59" s="5" t="inlineStr">
         <is>
           <t>Managing Director Sascha Bloemhoff, info@automotivecampus.com, +31 492 56 22 11.</t>
         </is>
@@ -6482,32 +6704,33 @@
           <t>info@mediapark.nl</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>+31 35 677 8080</t>
         </is>
       </c>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="R60" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R60" s="5" t="inlineStr">
+      <c r="S60" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S60" s="5" t="inlineStr">
+      <c r="T60" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T60" s="5" t="inlineStr">
+      <c r="U60" s="5" t="inlineStr">
         <is>
           <t>https://www.mediapark.nl/</t>
         </is>
       </c>
-      <c r="U60" s="5" t="inlineStr">
+      <c r="V60" s="5" t="inlineStr">
         <is>
           <t>Events calendar at mediapark.nl/events/. No named events contact found. Companies include NOS, RTL, NEP, EMG, ITV.</t>
         </is>
@@ -6572,27 +6795,28 @@
         </is>
       </c>
       <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R61" s="5" t="inlineStr">
+      <c r="S61" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S61" s="5" t="inlineStr">
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T61" s="5" t="inlineStr">
+      <c r="U61" s="5" t="inlineStr">
         <is>
           <t>https://www.theworkdistrict.nl/</t>
         </is>
       </c>
-      <c r="U61" s="5" t="inlineStr">
+      <c r="V61" s="5" t="inlineStr">
         <is>
           <t>Events page on site has the current calendar.</t>
         </is>
@@ -6657,27 +6881,28 @@
         </is>
       </c>
       <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr">
+      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R62" s="5" t="inlineStr">
+      <c r="S62" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S62" s="5" t="inlineStr">
+      <c r="T62" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T62" s="5" t="inlineStr">
+      <c r="U62" s="5" t="inlineStr">
         <is>
           <t>https://www.mind-labs.eu/en/</t>
         </is>
       </c>
-      <c r="U62" s="5" t="inlineStr">
+      <c r="V62" s="5" t="inlineStr">
         <is>
           <t>No named events manager on the homepage.</t>
         </is>
@@ -6749,32 +6974,33 @@
           <t>britt.vanbelkom@brightlands.com</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>+31 77 850 33 61</t>
         </is>
       </c>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="R63" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R63" s="5" t="inlineStr">
+      <c r="S63" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S63" s="5" t="inlineStr">
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T63" s="5" t="inlineStr">
+      <c r="U63" s="5" t="inlineStr">
         <is>
           <t>https://www.brightlands.com/en/campus-greenport-venlo/whom/brightlands-campus-greenport-venlo-community</t>
         </is>
       </c>
-      <c r="U63" s="5" t="inlineStr">
+      <c r="V63" s="5" t="inlineStr">
         <is>
           <t>Email shown as britt.vanbelkom [at] brightlands.com. General inbox brightlandsvenlo [at] brightlands.com.</t>
         </is>
@@ -6846,32 +7072,33 @@
           <t>robine.vandervelden@brightlands.com</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>+31 6 25 57 37 68</t>
         </is>
       </c>
-      <c r="Q64" s="5" t="inlineStr">
+      <c r="R64" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R64" s="5" t="inlineStr">
+      <c r="S64" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="T64" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T64" s="5" t="inlineStr">
+      <c r="U64" s="5" t="inlineStr">
         <is>
           <t>https://www.brightlands.com/en/maastricht-health-campus/contact/team-brightlands-maastricht-health-campus</t>
         </is>
       </c>
-      <c r="U64" s="5" t="inlineStr">
+      <c r="V64" s="5" t="inlineStr">
         <is>
           <t>Email shown obfuscated (at) in search result; phone is the COO's number from the team page. Yves Slenter, Community Development Manager (since Feb 2024) per search result. Mostly professional events.</t>
         </is>
@@ -6943,32 +7170,33 @@
           <t>anouk.eijkelberg@brightlands.com</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>+31 6 34377739</t>
         </is>
       </c>
-      <c r="Q65" s="5" t="inlineStr">
+      <c r="R65" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R65" s="5" t="inlineStr">
+      <c r="S65" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S65" s="5" t="inlineStr">
+      <c r="T65" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T65" s="5" t="inlineStr">
+      <c r="U65" s="5" t="inlineStr">
         <is>
           <t>https://www.brightlands.com/en/smart-services-campus/about/brightlands-smart-services-campus-community</t>
         </is>
       </c>
-      <c r="U65" s="5" t="inlineStr">
+      <c r="V65" s="5" t="inlineStr">
         <is>
           <t>Email shown as (at). Event Manager Barbera Sloos per search result (events.smartservices [at] brightlands.com).</t>
         </is>
@@ -7041,27 +7269,28 @@
       </c>
       <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr">
+      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R66" s="5" t="inlineStr">
+      <c r="S66" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S66" s="5" t="inlineStr">
+      <c r="T66" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T66" s="5" t="inlineStr">
+      <c r="U66" s="5" t="inlineStr">
         <is>
           <t>https://marineterrein.nl/en/collective/</t>
         </is>
       </c>
-      <c r="U66" s="5" t="inlineStr">
+      <c r="V66" s="5" t="inlineStr">
         <is>
           <t>Homepage has no email or phone; use the contact page. Sports-minded site (public swimming, fitness). Impact Hub is also here.</t>
         </is>
@@ -7130,27 +7359,28 @@
       <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="5" t="inlineStr"/>
       <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R67" s="5" t="inlineStr">
+      <c r="S67" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S67" s="5" t="inlineStr">
+      <c r="T67" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T67" s="5" t="inlineStr">
+      <c r="U67" s="5" t="inlineStr">
         <is>
           <t>https://tshcollab.com/en/amsterdam-city</t>
         </is>
       </c>
-      <c r="U67" s="5" t="inlineStr">
+      <c r="V67" s="5" t="inlineStr">
         <is>
           <t>Site fetch returned 503, details come from search results. Also a TSH Collab at Amsterdam West. Contact via the site form. Next door to Volkshotel on Wibautstraat.</t>
         </is>
@@ -7211,27 +7441,28 @@
       <c r="N68" s="5" t="inlineStr"/>
       <c r="O68" s="5" t="inlineStr"/>
       <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="5" t="inlineStr">
+      <c r="Q68" s="5" t="inlineStr"/>
+      <c r="R68" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R68" s="5" t="inlineStr">
+      <c r="S68" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S68" s="5" t="inlineStr">
+      <c r="T68" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T68" s="5" t="inlineStr">
+      <c r="U68" s="5" t="inlineStr">
         <is>
           <t>https://greenbusinessclub.nl/zuidas/over-ons/</t>
         </is>
       </c>
-      <c r="U68" s="5" t="inlineStr">
+      <c r="V68" s="5" t="inlineStr">
         <is>
           <t>Sustainability focus, not sport. Part of a national network of about 20 local Green Business Clubs. Contact details not retrieved.</t>
         </is>
@@ -7292,27 +7523,28 @@
       <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="inlineStr"/>
       <c r="P69" s="5" t="inlineStr"/>
-      <c r="Q69" s="5" t="inlineStr">
+      <c r="Q69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R69" s="5" t="inlineStr">
+      <c r="S69" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S69" s="5" t="inlineStr">
+      <c r="T69" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T69" s="5" t="inlineStr">
+      <c r="U69" s="5" t="inlineStr">
         <is>
           <t>https://www.amsterdamsciencepark.nl/contact/</t>
         </is>
       </c>
-      <c r="U69" s="5" t="inlineStr">
+      <c r="V69" s="5" t="inlineStr">
         <is>
           <t>Details come from a search snippet; page returned 404 when fetched. Sport is covered by USC Sportcentre Universum nearby.</t>
         </is>
@@ -7385,27 +7617,28 @@
       </c>
       <c r="O70" s="5" t="inlineStr"/>
       <c r="P70" s="5" t="inlineStr"/>
-      <c r="Q70" s="5" t="inlineStr">
+      <c r="Q70" s="5" t="inlineStr"/>
+      <c r="R70" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R70" s="5" t="inlineStr">
+      <c r="S70" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Marcel la Rose (Chairman (stepping down after 23 June; treasurer Esli Demirel))</t>
         </is>
       </c>
-      <c r="S70" s="5" t="inlineStr">
+      <c r="T70" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T70" s="5" t="inlineStr">
+      <c r="U70" s="5" t="inlineStr">
         <is>
           <t>https://www.westpoortondernemers.nl/</t>
         </is>
       </c>
-      <c r="U70" s="5" t="inlineStr">
+      <c r="V70" s="5" t="inlineStr">
         <is>
           <t>Mostly an advocacy group (accessibility, safety, area development). No sport events found, so low priority.</t>
         </is>
@@ -7474,27 +7707,28 @@
       <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="5" t="inlineStr"/>
       <c r="P71" s="5" t="inlineStr"/>
-      <c r="Q71" s="5" t="inlineStr">
+      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="R71" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R71" s="5" t="inlineStr">
+      <c r="S71" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S71" s="5" t="inlineStr">
+      <c r="T71" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T71" s="5" t="inlineStr">
+      <c r="U71" s="5" t="inlineStr">
         <is>
           <t>https://atlasarena.nl/community/</t>
         </is>
       </c>
-      <c r="U71" s="5" t="inlineStr">
+      <c r="V71" s="5" t="inlineStr">
         <is>
           <t>Already runs a volleyball tournament, so sport tournaments are accepted. Community manager not named on the page seen; check Contact page.</t>
         </is>
@@ -7562,32 +7796,33 @@
       <c r="M72" s="5" t="inlineStr"/>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="5" t="inlineStr">
+      <c r="P72" s="5" t="inlineStr"/>
+      <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>+31 (0)10 808 00 13</t>
         </is>
       </c>
-      <c r="Q72" s="5" t="inlineStr">
+      <c r="R72" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="R72" s="5" t="inlineStr">
+      <c r="S72" s="5" t="inlineStr">
         <is>
           <t>Call +31 (0)10 808 00 13 and ask for whoever runs community or tenant events.</t>
         </is>
       </c>
-      <c r="S72" s="5" t="inlineStr">
+      <c r="T72" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T72" s="5" t="inlineStr">
+      <c r="U72" s="5" t="inlineStr">
         <is>
           <t>https://cic.com/rotterdam/</t>
         </is>
       </c>
-      <c r="U72" s="5" t="inlineStr">
+      <c r="V72" s="5" t="inlineStr">
         <is>
           <t>Contact via form at cic.com/contact/. No named community manager published on the page. Large, event-heavy community, good target for an inter-company league.</t>
         </is>
@@ -7660,27 +7895,28 @@
       </c>
       <c r="O73" s="5" t="inlineStr"/>
       <c r="P73" s="5" t="inlineStr"/>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R73" s="5" t="inlineStr">
+      <c r="S73" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S73" s="5" t="inlineStr">
+      <c r="T73" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T73" s="5" t="inlineStr">
+      <c r="U73" s="5" t="inlineStr">
         <is>
           <t>https://www.kantorenparkrijnsweerd.nl/</t>
         </is>
       </c>
-      <c r="U73" s="5" t="inlineStr">
+      <c r="V73" s="5" t="inlineStr">
         <is>
           <t>Contact form only; names not shown on homepage. Sports strip suggests receptiveness to an after work football game.</t>
         </is>
@@ -7749,27 +7985,28 @@
       <c r="N74" s="5" t="inlineStr"/>
       <c r="O74" s="5" t="inlineStr"/>
       <c r="P74" s="5" t="inlineStr"/>
-      <c r="Q74" s="5" t="inlineStr">
+      <c r="Q74" s="5" t="inlineStr"/>
+      <c r="R74" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R74" s="5" t="inlineStr">
+      <c r="S74" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S74" s="5" t="inlineStr">
+      <c r="T74" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T74" s="5" t="inlineStr">
+      <c r="U74" s="5" t="inlineStr">
         <is>
           <t>https://workin.space/en/coworking/netherlands/limburg/maastricht-6200/the-social-hub-maastricht</t>
         </is>
       </c>
-      <c r="U74" s="5" t="inlineStr">
+      <c r="V74" s="5" t="inlineStr">
         <is>
           <t>Has a community and event manager role (job listing for an intern). Also operates in Rotterdam, Delft and Den Haag, so a group-level approach is possible.</t>
         </is>
@@ -7838,27 +8075,28 @@
       </c>
       <c r="O75" s="5" t="inlineStr"/>
       <c r="P75" s="5" t="inlineStr"/>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="Q75" s="5" t="inlineStr"/>
+      <c r="R75" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R75" s="5" t="inlineStr">
+      <c r="S75" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S75" s="5" t="inlineStr">
+      <c r="T75" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T75" s="5" t="inlineStr">
+      <c r="U75" s="5" t="inlineStr">
         <is>
           <t>https://www.spacesworks.com/amsterdam/zuidas/meeting-rooms/</t>
         </is>
       </c>
-      <c r="U75" s="5" t="inlineStr">
+      <c r="V75" s="5" t="inlineStr">
         <is>
           <t>No named person or direct email published; contact via Spaces form. Zuidas has several more Spaces centres (Zuidas II) and a business-club style member offer.</t>
         </is>
@@ -7923,27 +8161,28 @@
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr"/>
       <c r="P76" s="5" t="inlineStr"/>
-      <c r="Q76" s="5" t="inlineStr">
+      <c r="Q76" s="5" t="inlineStr"/>
+      <c r="R76" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R76" s="5" t="inlineStr">
+      <c r="S76" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S76" s="5" t="inlineStr">
+      <c r="T76" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T76" s="5" t="inlineStr">
+      <c r="U76" s="5" t="inlineStr">
         <is>
           <t>https://www.wework.com/buildings/strawinskylaan-4117--amsterdam</t>
         </is>
       </c>
-      <c r="U76" s="5" t="inlineStr">
+      <c r="V76" s="5" t="inlineStr">
         <is>
           <t>No local contact or email on page; the only phone listed is a US number, so left blank. Check that the location is still open before outreach.</t>
         </is>
@@ -8008,27 +8247,28 @@
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="inlineStr"/>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R77" s="5" t="inlineStr">
+      <c r="S77" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S77" s="5" t="inlineStr">
+      <c r="T77" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T77" s="5" t="inlineStr">
+      <c r="U77" s="5" t="inlineStr">
         <is>
           <t>https://flexifyhq.com/spaces/teleport-towers/</t>
         </is>
       </c>
-      <c r="U77" s="5" t="inlineStr">
+      <c r="V77" s="5" t="inlineStr">
         <is>
           <t>Weak lead: events evidence from third-party listings only; no community contact published. Sloterdijk station area.</t>
         </is>
@@ -8096,32 +8336,33 @@
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr"/>
-      <c r="P78" s="5" t="inlineStr">
+      <c r="P78" s="5" t="inlineStr"/>
+      <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>+31 20 225 0044</t>
         </is>
       </c>
-      <c r="Q78" s="5" t="inlineStr">
+      <c r="R78" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="R78" s="5" t="inlineStr">
+      <c r="S78" s="5" t="inlineStr">
         <is>
           <t>Call +31 20 225 0044 and ask for whoever runs community or tenant events.</t>
         </is>
       </c>
-      <c r="S78" s="5" t="inlineStr">
+      <c r="T78" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T78" s="5" t="inlineStr">
+      <c r="U78" s="5" t="inlineStr">
         <is>
           <t>https://copass.org/cospaces/merkspace-amstelveen</t>
         </is>
       </c>
-      <c r="U78" s="5" t="inlineStr">
+      <c r="V78" s="5" t="inlineStr">
         <is>
           <t>Event details are from press and directory sources, not verified on their own site (fetch failed). Tennis courts on site, so sports-friendly; check the site is still operating.</t>
         </is>
@@ -8193,32 +8434,33 @@
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr"/>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr"/>
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>+31 24 204 9060</t>
         </is>
       </c>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R79" s="5" t="inlineStr">
+      <c r="S79" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Yvette Akkermans-Hazekamp (Community Manager), or call +31 24 204 9060</t>
         </is>
       </c>
-      <c r="S79" s="5" t="inlineStr">
+      <c r="T79" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T79" s="5" t="inlineStr">
+      <c r="U79" s="5" t="inlineStr">
         <is>
           <t>https://noviotechcampus.com/</t>
         </is>
       </c>
-      <c r="U79" s="5" t="inlineStr">
+      <c r="V79" s="5" t="inlineStr">
         <is>
           <t>Community manager name from search results (not on fetched homepage); site email obfuscated, ask via campus inbox. Operator Kadans organises Meet &amp; Eat jointly.</t>
         </is>
@@ -8283,27 +8525,28 @@
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="inlineStr"/>
-      <c r="Q80" s="5" t="inlineStr">
+      <c r="Q80" s="5" t="inlineStr"/>
+      <c r="R80" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R80" s="5" t="inlineStr">
+      <c r="S80" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S80" s="5" t="inlineStr">
+      <c r="T80" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T80" s="5" t="inlineStr">
+      <c r="U80" s="5" t="inlineStr">
         <is>
           <t>https://www.dutchofficefund.nl/</t>
         </is>
       </c>
-      <c r="U80" s="5" t="inlineStr">
+      <c r="V80" s="5" t="inlineStr">
         <is>
           <t>Fund contact SupportTowerTen@cbreim.com (general). Zuidas location, near Mahler towers. Own community manager not identified.</t>
         </is>
@@ -8364,27 +8607,28 @@
       <c r="N81" s="5" t="inlineStr"/>
       <c r="O81" s="5" t="inlineStr"/>
       <c r="P81" s="5" t="inlineStr"/>
-      <c r="Q81" s="5" t="inlineStr">
+      <c r="Q81" s="5" t="inlineStr"/>
+      <c r="R81" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R81" s="5" t="inlineStr">
+      <c r="S81" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S81" s="5" t="inlineStr">
+      <c r="T81" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T81" s="5" t="inlineStr">
+      <c r="U81" s="5" t="inlineStr">
         <is>
           <t>https://www.wework.com/buildings/weteringschans-165--amsterdam</t>
         </is>
       </c>
-      <c r="U81" s="5" t="inlineStr">
+      <c r="V81" s="5" t="inlineStr">
         <is>
           <t>No local contact on page. Confirm the site is still operating. Lower priority than owner-run hubs.</t>
         </is>
@@ -8444,32 +8688,33 @@
       <c r="M82" s="5" t="inlineStr"/>
       <c r="N82" s="5" t="inlineStr"/>
       <c r="O82" s="5" t="inlineStr"/>
-      <c r="P82" s="5" t="inlineStr">
+      <c r="P82" s="5" t="inlineStr"/>
+      <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>*5850 (Mon-Fri 09:00-18:00)</t>
         </is>
       </c>
-      <c r="Q82" s="5" t="inlineStr">
+      <c r="R82" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="R82" s="5" t="inlineStr">
+      <c r="S82" s="5" t="inlineStr">
         <is>
           <t>Call *5850 (Mon-Fri 09:00-18:00) and ask for whoever runs community or tenant events.</t>
         </is>
       </c>
-      <c r="S82" s="5" t="inlineStr">
+      <c r="T82" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T82" s="5" t="inlineStr">
+      <c r="U82" s="5" t="inlineStr">
         <is>
           <t>https://www.mindspace.me/amsterdam/danzigerkade/</t>
         </is>
       </c>
-      <c r="U82" s="5" t="inlineStr">
+      <c r="V82" s="5" t="inlineStr">
         <is>
           <t>Mindspace has about 7 Amsterdam sites (Dam, Herengracht, Nieuwezijds Voorburgwal 296-298, Sophialaan 21, Wenckebachweg 90 and 100, Danzigerkade). Phone is a short number as published. Mostly managed private offices.</t>
         </is>
@@ -8530,27 +8775,28 @@
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="5" t="inlineStr"/>
       <c r="P83" s="5" t="inlineStr"/>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R83" s="5" t="inlineStr">
+      <c r="S83" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S83" s="5" t="inlineStr">
+      <c r="T83" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T83" s="5" t="inlineStr">
+      <c r="U83" s="5" t="inlineStr">
         <is>
           <t>https://www.coworker.com/netherlands/amsterdam/the-thinking-hut</t>
         </is>
       </c>
-      <c r="U83" s="5" t="inlineStr">
+      <c r="V83" s="5" t="inlineStr">
         <is>
           <t>Own site could not be fetched, so no email taken; a search snippet cited info@thethinkinghut.com but it is unverified. Small, international freelancer crowd.</t>
         </is>
@@ -8607,27 +8853,28 @@
       <c r="N84" s="5" t="inlineStr"/>
       <c r="O84" s="5" t="inlineStr"/>
       <c r="P84" s="5" t="inlineStr"/>
-      <c r="Q84" s="5" t="inlineStr">
+      <c r="Q84" s="5" t="inlineStr"/>
+      <c r="R84" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R84" s="5" t="inlineStr">
+      <c r="S84" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S84" s="5" t="inlineStr">
+      <c r="T84" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T84" s="5" t="inlineStr">
+      <c r="U84" s="5" t="inlineStr">
         <is>
           <t>https://www.spacesworks.com/en/nl/3178</t>
         </is>
       </c>
-      <c r="U84" s="5" t="inlineStr">
+      <c r="V84" s="5" t="inlineStr">
         <is>
           <t>From search snippet only; page not fetchable. Weak evidence of events.</t>
         </is>
@@ -8687,32 +8934,33 @@
       <c r="M85" s="5" t="inlineStr"/>
       <c r="N85" s="5" t="inlineStr"/>
       <c r="O85" s="5" t="inlineStr"/>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="P85" s="5" t="inlineStr"/>
+      <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>+31 10 252 44 72</t>
         </is>
       </c>
-      <c r="Q85" s="5" t="inlineStr">
+      <c r="R85" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="R85" s="5" t="inlineStr">
+      <c r="S85" s="5" t="inlineStr">
         <is>
           <t>Call +31 10 252 44 72 and ask for whoever runs community or tenant events.</t>
         </is>
       </c>
-      <c r="S85" s="5" t="inlineStr">
+      <c r="T85" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T85" s="5" t="inlineStr">
+      <c r="U85" s="5" t="inlineStr">
         <is>
           <t>https://www.rdmrotterdam.nl/en/meet</t>
         </is>
       </c>
-      <c r="U85" s="5" t="inlineStr">
+      <c r="V85" s="5" t="inlineStr">
         <is>
           <t>Email on the page was garbled in extraction (communicatie at rdmrotterdam.nl); not recorded. Mostly venue and innovation programme, tenant social events unproven.</t>
         </is>
@@ -8773,27 +9021,28 @@
       <c r="N86" s="5" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
       <c r="P86" s="5" t="inlineStr"/>
-      <c r="Q86" s="5" t="inlineStr">
+      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="R86" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R86" s="5" t="inlineStr">
+      <c r="S86" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S86" s="5" t="inlineStr">
+      <c r="T86" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T86" s="5" t="inlineStr">
+      <c r="U86" s="5" t="inlineStr">
         <is>
           <t>https://www.matrixic.nl/en/community/</t>
         </is>
       </c>
-      <c r="U86" s="5" t="inlineStr">
+      <c r="V86" s="5" t="inlineStr">
         <is>
           <t>Site fetch failed; info from Amsterdam Science Park news. Tenants include Qualcomm and Photanol. Pitch together with Amsterdam Science Park.</t>
         </is>
@@ -8861,32 +9110,33 @@
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr"/>
-      <c r="P87" s="5" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr"/>
+      <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>+31 6 38166263</t>
         </is>
       </c>
-      <c r="Q87" s="5" t="inlineStr">
+      <c r="R87" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R87" s="5" t="inlineStr">
+      <c r="S87" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Nabile Benali (Campus Manager), or call +31 6 38166263</t>
         </is>
       </c>
-      <c r="S87" s="5" t="inlineStr">
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T87" s="5" t="inlineStr">
+      <c r="U87" s="5" t="inlineStr">
         <is>
           <t>https://hsdcampus.nl/en/</t>
         </is>
       </c>
-      <c r="U87" s="5" t="inlineStr">
+      <c r="V87" s="5" t="inlineStr">
         <is>
           <t>Main HSD phone +31 70 204 5180; site says currently contactable by phone only. Press contact Chantal de Niet (Communications Manager).</t>
         </is>
@@ -8947,27 +9197,28 @@
       <c r="N88" s="5" t="inlineStr"/>
       <c r="O88" s="5" t="inlineStr"/>
       <c r="P88" s="5" t="inlineStr"/>
-      <c r="Q88" s="5" t="inlineStr">
+      <c r="Q88" s="5" t="inlineStr"/>
+      <c r="R88" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R88" s="5" t="inlineStr">
+      <c r="S88" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S88" s="5" t="inlineStr">
+      <c r="T88" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T88" s="5" t="inlineStr">
+      <c r="U88" s="5" t="inlineStr">
         <is>
           <t>https://playgroundcoworking.nl/</t>
         </is>
       </c>
-      <c r="U88" s="5" t="inlineStr">
+      <c r="V88" s="5" t="inlineStr">
         <is>
           <t>One minute from Arnhem Centraal. Contact via form only.</t>
         </is>
@@ -9028,27 +9279,28 @@
       <c r="N89" s="5" t="inlineStr"/>
       <c r="O89" s="5" t="inlineStr"/>
       <c r="P89" s="5" t="inlineStr"/>
-      <c r="Q89" s="5" t="inlineStr">
+      <c r="Q89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R89" s="5" t="inlineStr">
+      <c r="S89" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S89" s="5" t="inlineStr">
+      <c r="T89" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T89" s="5" t="inlineStr">
+      <c r="U89" s="5" t="inlineStr">
         <is>
           <t>https://www.regus.com/en-gb/netherlands/amstelveen/parktoren-5080</t>
         </is>
       </c>
-      <c r="U89" s="5" t="inlineStr">
+      <c r="V89" s="5" t="inlineStr">
         <is>
           <t>Weak events evidence. Included as the main Amstelveen Regus site. Spaces also has Amstelveen centres.</t>
         </is>
@@ -9109,27 +9361,28 @@
       <c r="N90" s="5" t="inlineStr"/>
       <c r="O90" s="5" t="inlineStr"/>
       <c r="P90" s="5" t="inlineStr"/>
-      <c r="Q90" s="5" t="inlineStr">
+      <c r="Q90" s="5" t="inlineStr"/>
+      <c r="R90" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R90" s="5" t="inlineStr">
+      <c r="S90" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S90" s="5" t="inlineStr">
+      <c r="T90" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T90" s="5" t="inlineStr">
+      <c r="U90" s="5" t="inlineStr">
         <is>
           <t>https://www.launchpad023.nl/</t>
         </is>
       </c>
-      <c r="U90" s="5" t="inlineStr">
+      <c r="V90" s="5" t="inlineStr">
         <is>
           <t>Located in the Waarderpolder. Events calendar at launchpad023.nl/events. No email or phone on homepage.</t>
         </is>
@@ -9189,32 +9442,33 @@
       <c r="M91" s="5" t="inlineStr"/>
       <c r="N91" s="5" t="inlineStr"/>
       <c r="O91" s="5" t="inlineStr"/>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="P91" s="5" t="inlineStr"/>
+      <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>06 109 4444 0</t>
         </is>
       </c>
-      <c r="Q91" s="5" t="inlineStr">
+      <c r="R91" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="R91" s="5" t="inlineStr">
+      <c r="S91" s="5" t="inlineStr">
         <is>
           <t>Call 06 109 4444 0 and ask for whoever runs community or tenant events.</t>
         </is>
       </c>
-      <c r="S91" s="5" t="inlineStr">
+      <c r="T91" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T91" s="5" t="inlineStr">
+      <c r="U91" s="5" t="inlineStr">
         <is>
           <t>https://startupnijmegen.nl/</t>
         </is>
       </c>
-      <c r="U91" s="5" t="inlineStr">
+      <c r="V91" s="5" t="inlineStr">
         <is>
           <t>Email obscured on fetched page. Team page at /team/. Next to Nijmegen central station.</t>
         </is>
@@ -9283,27 +9537,28 @@
       </c>
       <c r="O92" s="5" t="inlineStr"/>
       <c r="P92" s="5" t="inlineStr"/>
-      <c r="Q92" s="5" t="inlineStr">
+      <c r="Q92" s="5" t="inlineStr"/>
+      <c r="R92" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R92" s="5" t="inlineStr">
+      <c r="S92" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Donna Algra (Business Development Manager (joining enquiries; not the events lead))</t>
         </is>
       </c>
-      <c r="S92" s="5" t="inlineStr">
+      <c r="T92" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T92" s="5" t="inlineStr">
+      <c r="U92" s="5" t="inlineStr">
         <is>
           <t>https://www.pivotpark.com/join-us/</t>
         </is>
       </c>
-      <c r="U92" s="5" t="inlineStr">
+      <c r="V92" s="5" t="inlineStr">
         <is>
           <t>pivotpark.com returned 503 on fetch; details from search snippets. Address from general knowledge, unverified. Community manager name not found.</t>
         </is>
@@ -9371,32 +9626,33 @@
         </is>
       </c>
       <c r="O93" s="5" t="inlineStr"/>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="P93" s="5" t="inlineStr"/>
+      <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>+31 76 369 0699</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr">
+      <c r="R93" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R93" s="5" t="inlineStr">
+      <c r="S93" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Denise Welten (Community Manager), or call +31 76 369 0699</t>
         </is>
       </c>
-      <c r="S93" s="5" t="inlineStr">
+      <c r="T93" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T93" s="5" t="inlineStr">
+      <c r="U93" s="5" t="inlineStr">
         <is>
           <t>https://officestories.nl/</t>
         </is>
       </c>
-      <c r="U93" s="5" t="inlineStr">
+      <c r="V93" s="5" t="inlineStr">
         <is>
           <t>Small creative-entrepreneur community. Email obscured on fetched page.</t>
         </is>
@@ -9468,32 +9724,33 @@
           <t>info@zuidasrun.nl</t>
         </is>
       </c>
-      <c r="P94" s="5" t="inlineStr">
+      <c r="P94" s="5" t="inlineStr"/>
+      <c r="Q94" s="5" t="inlineStr">
         <is>
           <t>020 496 91 73</t>
         </is>
       </c>
-      <c r="Q94" s="5" t="inlineStr">
+      <c r="R94" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R94" s="5" t="inlineStr">
+      <c r="S94" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S94" s="5" t="inlineStr">
+      <c r="T94" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T94" s="5" t="inlineStr">
+      <c r="U94" s="5" t="inlineStr">
         <is>
           <t>https://truetribezuidasrun.nl/</t>
         </is>
       </c>
-      <c r="U94" s="5" t="inlineStr">
+      <c r="V94" s="5" t="inlineStr">
         <is>
           <t>Partner angle: same audience (Zuidas employers) as a weekly football offer. Event date 12 June 2026; 2027 pre-registration open. | also: https://zuidas.nl/en/activity/zuidas-run/</t>
         </is>
@@ -9565,32 +9822,33 @@
           <t>info@ballie.nl</t>
         </is>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr"/>
+      <c r="Q95" s="5" t="inlineStr">
         <is>
           <t>+31 6 43 89 97 09</t>
         </is>
       </c>
-      <c r="Q95" s="5" t="inlineStr">
+      <c r="R95" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R95" s="5" t="inlineStr">
+      <c r="S95" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S95" s="5" t="inlineStr">
+      <c r="T95" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T95" s="5" t="inlineStr">
+      <c r="U95" s="5" t="inlineStr">
         <is>
           <t>https://ballie.nl/contact/</t>
         </is>
       </c>
-      <c r="U95" s="5" t="inlineStr">
+      <c r="V95" s="5" t="inlineStr">
         <is>
           <t>Direct competitor in the northern and eastern Netherlands; KvK 99247275. WhatsApp is the preferred contact route.</t>
         </is>
@@ -9662,32 +9920,33 @@
           <t>jouw@odiv.nl</t>
         </is>
       </c>
-      <c r="P96" s="5" t="inlineStr">
+      <c r="P96" s="5" t="inlineStr"/>
+      <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>030 227 05 77</t>
         </is>
       </c>
-      <c r="Q96" s="5" t="inlineStr">
+      <c r="R96" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R96" s="5" t="inlineStr">
+      <c r="S96" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S96" s="5" t="inlineStr">
+      <c r="T96" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T96" s="5" t="inlineStr">
+      <c r="U96" s="5" t="inlineStr">
         <is>
           <t>https://odiv.nl/footy/</t>
         </is>
       </c>
-      <c r="U96" s="5" t="inlineStr">
+      <c r="V96" s="5" t="inlineStr">
         <is>
           <t>One-day tournament run by a marketing agency; partner or competitor in Utrecht, and a possible referral source for SME teams.</t>
         </is>
@@ -9763,32 +10022,33 @@
           <t>info@zomercompetitie.com</t>
         </is>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="P97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>+31 6 38824408</t>
         </is>
       </c>
-      <c r="Q97" s="5" t="inlineStr">
+      <c r="R97" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R97" s="5" t="inlineStr">
+      <c r="S97" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S97" s="5" t="inlineStr">
+      <c r="T97" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T97" s="5" t="inlineStr">
+      <c r="U97" s="5" t="inlineStr">
         <is>
           <t>https://www.zomercompetitie.com/contact/</t>
         </is>
       </c>
-      <c r="U97" s="5" t="inlineStr">
+      <c r="V97" s="5" t="inlineStr">
         <is>
           <t>Direct competitor / partner for company football. Women-only football in Amsterdam. Fourth city planned for 2027. Seasonal (spring, summer, autumn) rather than weekly. Alternative phone on Hello Zuidas listing: 06 41875286.</t>
         </is>
@@ -9864,32 +10124,33 @@
           <t>max.beulink@lechampion.nl</t>
         </is>
       </c>
-      <c r="P98" s="5" t="inlineStr">
+      <c r="P98" s="5" t="inlineStr"/>
+      <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>06 81 26 88 01</t>
         </is>
       </c>
-      <c r="Q98" s="5" t="inlineStr">
+      <c r="R98" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R98" s="5" t="inlineStr">
+      <c r="S98" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S98" s="5" t="inlineStr">
+      <c r="T98" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T98" s="5" t="inlineStr">
+      <c r="U98" s="5" t="inlineStr">
         <is>
           <t>https://www.lechampion.nl/businessteams</t>
         </is>
       </c>
-      <c r="U98" s="5" t="inlineStr">
+      <c r="V98" s="5" t="inlineStr">
         <is>
           <t>Partner angle only (running, once a year); useful for cross-promotion to company HR contacts. Organiser address not shown on the pages read.</t>
         </is>
@@ -9961,32 +10222,33 @@
           <t>zotica.evans@Corporate-games.com</t>
         </is>
       </c>
-      <c r="P99" s="5" t="inlineStr">
+      <c r="P99" s="5" t="inlineStr"/>
+      <c r="Q99" s="5" t="inlineStr">
         <is>
           <t>06-39 34 10 40</t>
         </is>
       </c>
-      <c r="Q99" s="5" t="inlineStr">
+      <c r="R99" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R99" s="5" t="inlineStr">
+      <c r="S99" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S99" s="5" t="inlineStr">
+      <c r="T99" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T99" s="5" t="inlineStr">
+      <c r="U99" s="5" t="inlineStr">
         <is>
           <t>https://magazines.onderneemin.nl/onderneem-in-haarlemmermeer-04/corporate-games</t>
         </is>
       </c>
-      <c r="U99" s="5" t="inlineStr">
+      <c r="V99" s="5" t="inlineStr">
         <is>
           <t>Information dates from 2019; no later Dutch edition confirmed. Check whether it is still active before approaching.</t>
         </is>
@@ -10051,27 +10313,28 @@
       <c r="N100" s="5" t="inlineStr"/>
       <c r="O100" s="5" t="inlineStr"/>
       <c r="P100" s="5" t="inlineStr"/>
-      <c r="Q100" s="5" t="inlineStr">
+      <c r="Q100" s="5" t="inlineStr"/>
+      <c r="R100" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R100" s="5" t="inlineStr">
+      <c r="S100" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S100" s="5" t="inlineStr">
+      <c r="T100" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T100" s="5" t="inlineStr">
+      <c r="U100" s="5" t="inlineStr">
         <is>
           <t>https://www.teamtoc.nl/evenementen/european-company-sport-games-2022</t>
         </is>
       </c>
-      <c r="U100" s="5" t="inlineStr">
+      <c r="V100" s="5" t="inlineStr">
         <is>
           <t>Contact via form at teamtoc.nl/contact. Named people on page: Martine Schuijer (director NLOM! Foundation), Musa Lami (Secretary General EFCS). Sport&amp;zaken is the bedrijfssport body linked to NOC*NSF and sports federations. Partner angle.</t>
         </is>
@@ -10132,27 +10395,28 @@
       <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="5" t="inlineStr"/>
       <c r="P101" s="5" t="inlineStr"/>
-      <c r="Q101" s="5" t="inlineStr">
+      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="R101" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R101" s="5" t="inlineStr">
+      <c r="S101" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S101" s="5" t="inlineStr">
+      <c r="T101" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T101" s="5" t="inlineStr">
+      <c r="U101" s="5" t="inlineStr">
         <is>
           <t>https://www.footy.nl/bedrijfsvoetbal/</t>
         </is>
       </c>
-      <c r="U101" s="5" t="inlineStr">
+      <c r="V101" s="5" t="inlineStr">
         <is>
           <t>Direct competitor. Pages returned no content when fetched, so only the search listing is confirmed. Contact details to be found manually.</t>
         </is>
@@ -10221,27 +10485,28 @@
         </is>
       </c>
       <c r="P102" s="5" t="inlineStr"/>
-      <c r="Q102" s="5" t="inlineStr">
+      <c r="Q102" s="5" t="inlineStr"/>
+      <c r="R102" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R102" s="5" t="inlineStr">
+      <c r="S102" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S102" s="5" t="inlineStr">
+      <c r="T102" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T102" s="5" t="inlineStr">
+      <c r="U102" s="5" t="inlineStr">
         <is>
           <t>http://deleague.nl/?page_id=12</t>
         </is>
       </c>
-      <c r="U102" s="5" t="inlineStr">
+      <c r="V102" s="5" t="inlineStr">
         <is>
           <t>Direct competitor (indoor futsal, Amsterdam). Details come from a search snippet; the site did not load when fetched.</t>
         </is>
@@ -10318,34 +10583,35 @@
         </is>
       </c>
       <c r="P103" s="5" t="inlineStr"/>
-      <c r="Q103" s="5" t="inlineStr">
+      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="R103" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R103" s="5" t="inlineStr">
+      <c r="S103" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S103" s="5" t="inlineStr">
+      <c r="T103" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T103" s="5" t="inlineStr">
+      <c r="U103" s="5" t="inlineStr">
         <is>
           <t>https://amsterdam.impacthub.net/what-we-do/our-team/</t>
         </is>
       </c>
-      <c r="U103" s="5" t="inlineStr">
+      <c r="V103" s="5" t="inlineStr">
         <is>
           <t>Emily Rendel is Start-up Ecosystem Coordinator on the same team page. Contact page says there is currently no landline. Located on Marineterrein, so can be pitched together with the Marineterrein row.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U103"/>
+  <autoFilter ref="A1:V103"/>
   <conditionalFormatting sqref="B2:B103">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B2="A"</formula>
@@ -10364,8 +10630,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="S2:S103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"To do,Contacted,Replied,Call booked,Not interested"</formula1>
+    <dataValidation sqref="T2:T103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Draft ready,To do,Contacted,Sent,Replied,Call booked,Not interested"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10378,7 +10644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10396,12 +10662,13 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10482,30 +10749,35 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
+          <t>Gmail draft</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Next step</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -10587,30 +10859,35 @@
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
+          <t>r8712680440305499555</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
           <t>070-511 23 87</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
           <t>https://vasakronan.se/fastigheter/katla-1-14532/hyresgastinfo/</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>Property manager, not events. Also Karl Lindgren, Commercial Manager Office, karl.lindgren@vasakronan.se, 070-540 37 25 (Kista contact on Vasakronan article).</t>
         </is>
@@ -10682,28 +10959,33 @@
           <t>info@lyckostaden.se</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>r-5782491926410639005</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
           <t>https://thekloud.se/en/we-run-kista/</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>Contact email from search snippet for We Run Kista. Outdoor sports surface already exists, strong partner fit.</t>
         </is>
@@ -10777,30 +11059,35 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
+          <t>r-4934139303058039382</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
           <t>08-22 31 01</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
           <t>https://cityisamverkan.se/om-oss/</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Network of retail and property owners, not sports. Could be a door-opener to member landlords.</t>
         </is>
@@ -10880,32 +11167,33 @@
           <t>michaela.linden@al.se</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>073-983 21 11</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S5" s="5" t="inlineStr">
         <is>
+          <t>Not drafted: owner Atrium Ljungberg also runs A House (already contacted, on the suppression list) and the contact is a leasing manager. Check with the team first.</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>https://www.al.se/sicklacentral/</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>Leasing contact. Second: Josefine Hjalmarsson, 070-861 99 85, josefine.hjalmarsson@al.se. Indoor football centre via Skills Academy (info@al.se, 08-615 89 00). Opened Sept 2025.</t>
         </is>
@@ -10977,28 +11265,33 @@
           <t>info@stenbeckstorg.se</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>r2759758805361516818</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
           <t>https://stenbeckstorg.se/</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>Open to organisers who want to run activities at the square; opened 14 Feb 2025.</t>
         </is>
@@ -11072,30 +11365,35 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
+          <t>r-3180413119398861486</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
           <t>+46 70 024 74 36</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
           <t>https://www.startuppeople.com/</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Physical coworking ceased in 2020; now digital-first. Phone from search result. Weak fit.</t>
         </is>
@@ -11169,30 +11467,35 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
+          <t>r5480753709205391672</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
           <t>+46 8 684 564 64</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
           <t>https://fabrikenevent.se/en/</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>Also an event venue operator. No community manager named. | also: hello@fabrikenevent.se; https://fabrikenevent.se/en/</t>
         </is>
@@ -11268,28 +11571,33 @@
           <t>info@unitedspaces.se</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>r8808577102281336719</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>Email first (draft can be prepared), follow up on LinkedIn after 7 days.</t>
-        </is>
-      </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Draft ready in Gmail (created 2 Oct). Review, then send or schedule from the Gmail screen, ideally 9:00 to 10:00 local time. Follow up after 7 days if no reply.</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
+          <t>Draft ready</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
           <t>https://www.unitedspaces.com/en/</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>Chain: one head-office conversation could cover many Stockholm sites. Exact site addresses not verified.</t>
         </is>
@@ -11362,27 +11670,28 @@
         </is>
       </c>
       <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>https://ssci.se/en/whats</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>Foundation owned by city, region, universities. Christina Jagare email: christina.jagare@ssci.se (newsletter tips).</t>
         </is>
@@ -11446,32 +11755,33 @@
           <t>co@profi.se</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>+46 702 833 892</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>https://careofworkspace.se/kunskapsbank/coworking-i-kista-natverka-med-techbolag-i-stockholms-innovationscentrum/</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Exact address not verified. United Spaces and Helio also have Kista sites.</t>
         </is>
@@ -11543,32 +11853,33 @@
           <t>ivar.bjorkman@openlab.se</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>+46736441413</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R12" s="5" t="inlineStr">
+      <c r="S12" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S12" s="5" t="inlineStr">
+      <c r="T12" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr">
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>https://openlabsthlm.se/contact/</t>
         </is>
       </c>
-      <c r="U12" s="5" t="inlineStr">
+      <c r="V12" s="5" t="inlineStr">
         <is>
           <t>Innovation Managers also listed (e.g. Ida Niskanen, Communications Manager, ida.niskanen@openlab.se). Weak evidence of social events.</t>
         </is>
@@ -11633,27 +11944,28 @@
         </is>
       </c>
       <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>https://events.sting.co/</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>Startup incubator; modest fit.</t>
         </is>
@@ -11725,32 +12037,33 @@
           <t>matilda@epicenterstockholm.com</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>08-459 30 60</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R14" s="5" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr">
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>https://weareepicenter.com/stockholm/community-activities/</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>General inbox hello@epicenterstockholm.com; Country Manager Oskar Gillström (gillstrom@epicenterstockholm.com). Community app for events.</t>
         </is>
@@ -11815,27 +12128,28 @@
         </is>
       </c>
       <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>https://sjostadsnytt.se/foretagare/</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>Contact is the local newspaper editorial inbox. Landlord founders (Fabege, Vasakronan) are also targets themselves.</t>
         </is>
@@ -11899,32 +12213,33 @@
           <t>hej@landskapet.nu</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>08-716 00 25</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R16" s="5" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>Email, follow up once after 7 days.</t>
         </is>
       </c>
-      <c r="S16" s="5" t="inlineStr">
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>https://landskapet.nu/coworking-i-nacka/</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>Weak events evidence.</t>
         </is>
@@ -11989,27 +12304,28 @@
       <c r="N17" s="5" t="inlineStr"/>
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>https://www.kiinnovation.se/community/</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="V17" s="5" t="inlineStr">
         <is>
           <t>Networking-style events, not sport. Contact form only on site.</t>
         </is>
@@ -12078,27 +12394,28 @@
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr">
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R18" s="5" t="inlineStr">
+      <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S18" s="5" t="inlineStr">
+      <c r="T18" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>https://kistasciencecity.com/about-us/</t>
         </is>
       </c>
-      <c r="U18" s="5" t="inlineStr">
+      <c r="V18" s="5" t="inlineStr">
         <is>
           <t>Contact page not fetched (kista.com returned 503). Postcode generic for Kista.</t>
         </is>
@@ -12174,32 +12491,33 @@
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr"/>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>08-600 68 93</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Marie Ekberg (Market Area Manager), or call 08-600 68 93</t>
         </is>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>https://www.amffastigheter.se/stockholm-city/urban-escape/</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>Also Mikael Wallgren, Office Leasing / Acting Property Manager, 070-812 12 13. Gallerian mall at centre.</t>
         </is>
@@ -12264,27 +12582,28 @@
       <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="T20" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>https://vasakronan.se/kontorserbjudande/lagen/hotorgsskraporna/</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="V20" s="5" t="inlineStr">
         <is>
           <t>Page refers to customer service only. Sergelkonferensen member club for tenants. Inter-company ping-pong shows appetite for company-vs-company formats.</t>
         </is>
@@ -12353,27 +12672,28 @@
       <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S21" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>https://www.humlegarden.se/hallbarhet/social-hallbarhet/</t>
         </is>
       </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>Customer service weekdays 08-17. Meeting spaces T-House (Engelbrektsplan) and Origo (Solna).</t>
         </is>
@@ -12442,27 +12762,28 @@
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R22" s="5" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S22" s="5" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T22" s="5" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>https://www.workthere.com/spaces/wework-urban-escape/</t>
         </is>
       </c>
-      <c r="U22" s="5" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>Also WeWork Regeringsgatan 29. Based on search summaries; no direct contact found. Epicenter is on the same street.</t>
         </is>
@@ -12527,27 +12848,28 @@
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R23" s="5" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S23" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T23" s="5" t="inlineStr">
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>https://www.knackeriet.se/</t>
         </is>
       </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="V23" s="5" t="inlineStr">
         <is>
           <t>Small community; no email published on fetched page. Already has a running club.</t>
         </is>
@@ -12608,27 +12930,28 @@
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R24" s="5" t="inlineStr">
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S24" s="5" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T24" s="5" t="inlineStr">
+      <c r="U24" s="5" t="inlineStr">
         <is>
           <t>https://dweller.se/coworkingkartan/the-park/forskaren</t>
         </is>
       </c>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>Website thepark.se. Instagram @theparkco. Data is from a third-party directory.</t>
         </is>
@@ -12689,27 +13012,28 @@
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R25" s="5" t="inlineStr">
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S25" s="5" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T25" s="5" t="inlineStr">
+      <c r="U25" s="5" t="inlineStr">
         <is>
           <t>https://www.hagastaden.se/en/about-hagastaden/</t>
         </is>
       </c>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>Site gave no individual contacts. Atrium Ljungberg general: info@al.se, 08-615 89 00. Strong growth over next years.</t>
         </is>
@@ -12770,27 +13094,28 @@
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R26" s="5" t="inlineStr">
+      <c r="S26" s="5" t="inlineStr">
         <is>
           <t>Send the short pitch through their website contact form.</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr">
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T26" s="5" t="inlineStr">
+      <c r="U26" s="5" t="inlineStr">
         <is>
           <t>https://thingstockholm.com/</t>
         </is>
       </c>
-      <c r="U26" s="5" t="inlineStr">
+      <c r="V26" s="5" t="inlineStr">
         <is>
           <t>Deep tech; corporate members could join leagues. No contact details on fetched page. Address from search result.</t>
         </is>
@@ -12859,27 +13184,28 @@
       </c>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="R27" s="5" t="inlineStr">
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM to Cathy (Office Manager (profile 'Meet Cathy'; surname not given))</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T27" s="5" t="inlineStr">
+      <c r="U27" s="5" t="inlineStr">
         <is>
           <t>https://www.embassy.house/en/news</t>
         </is>
       </c>
-      <c r="U27" s="5" t="inlineStr">
+      <c r="V27" s="5" t="inlineStr">
         <is>
           <t>No email fetched. Exact street address not verified.</t>
         </is>
@@ -12952,27 +13278,28 @@
         </is>
       </c>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R28" s="5" t="inlineStr">
+      <c r="S28" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S28" s="5" t="inlineStr">
+      <c r="T28" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T28" s="5" t="inlineStr">
+      <c r="U28" s="5" t="inlineStr">
         <is>
           <t>https://midnattsloppet.com/en/company-midnattsloppet/company-stockholm/</t>
         </is>
       </c>
-      <c r="U28" s="5" t="inlineStr">
+      <c r="V28" s="5" t="inlineStr">
         <is>
           <t>Partner angle: companies already form teams here, a football league could be a complementary offer.</t>
         </is>
@@ -13041,27 +13368,28 @@
         </is>
       </c>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R29" s="5" t="inlineStr">
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S29" s="5" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T29" s="5" t="inlineStr">
+      <c r="U29" s="5" t="inlineStr">
         <is>
           <t>https://www.korpen.se/korpenstockholm/aktiviteter/fotboll/seriespel/foretag/</t>
         </is>
       </c>
-      <c r="U29" s="5" t="inlineStr">
+      <c r="V29" s="5" t="inlineStr">
         <is>
           <t>Direct competitor / possible partner: already runs company football league in Stockholm. Pitches: Ostermalms IP, Ostra Reals BP, Johannes BP. | also: foretag@korpenstockholm.se; https://www.korpen.se/korpenstockholm/foretagsidrott/</t>
         </is>
@@ -13122,27 +13450,28 @@
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>Contact form</t>
         </is>
       </c>
-      <c r="R30" s="5" t="inlineStr">
+      <c r="S30" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S30" s="5" t="inlineStr">
+      <c r="T30" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr">
+      <c r="U30" s="5" t="inlineStr">
         <is>
           <t>https://foretagssm.se/kontakt/</t>
         </is>
       </c>
-      <c r="U30" s="5" t="inlineStr">
+      <c r="V30" s="5" t="inlineStr">
         <is>
           <t>Competitor / partner angle. Contact page exists but no direct details were captured.</t>
         </is>
@@ -13203,27 +13532,28 @@
         </is>
       </c>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="R31" s="5" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>Partner / competitor angle: offer FC Urban as pitch and player supplier for their company competitions, or extra weekly games for their teams.</t>
         </is>
       </c>
-      <c r="S31" s="5" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T31" s="5" t="inlineStr">
+      <c r="U31" s="5" t="inlineStr">
         <is>
           <t>https://blodomloppet.se/vara-lopp/stockholm/vanliga-fragor/</t>
         </is>
       </c>
-      <c r="U31" s="5" t="inlineStr">
+      <c r="V31" s="5" t="inlineStr">
         <is>
           <t>Contact for 50+ participant company bookings. National office: kansli@blodomloppet.se.</t>
         </is>
@@ -13303,32 +13633,33 @@
           <t>jeanette.nyroos@fabege.se</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>08-555 148 00</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="inlineStr">
+      <c r="R32" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R32" s="5" t="inlineStr">
+      <c r="S32" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S32" s="5" t="inlineStr">
+      <c r="T32" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T32" s="5" t="inlineStr">
+      <c r="U32" s="5" t="inlineStr">
         <is>
           <t>https://www.fabege.se/en/our-city-districts/solna/arenastaden/</t>
         </is>
       </c>
-      <c r="U32" s="5" t="inlineStr">
+      <c r="V32" s="5" t="inlineStr">
         <is>
           <t>Leasing contact only, not an events manager. General inbox info@fabege.se. Fabege app for meeting room booking. Strawberry Arena in district.</t>
         </is>
@@ -13409,27 +13740,28 @@
         </is>
       </c>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S33" s="5" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T33" s="5" t="inlineStr">
+      <c r="U33" s="5" t="inlineStr">
         <is>
           <t>https://www.norrsken.org/stockholm</t>
         </is>
       </c>
-      <c r="U33" s="5" t="inlineStr">
+      <c r="V33" s="5" t="inlineStr">
         <is>
           <t>Already has a run club; members are impact startups. Member portal on OfficeRND.</t>
         </is>
@@ -13505,32 +13837,33 @@
           <t>Lennart.Oberg@fabege.se</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>+46 70 678 01 89</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="R34" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R34" s="5" t="inlineStr">
+      <c r="S34" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="T34" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr">
+      <c r="U34" s="5" t="inlineStr">
         <is>
           <t>https://www.fabege.se/har-finns-vi/solna/solna-business-park/</t>
         </is>
       </c>
-      <c r="U34" s="5" t="inlineStr">
+      <c r="V34" s="5" t="inlineStr">
         <is>
           <t>Leasing contact, not an events person. Padel / pickleball on site.</t>
         </is>
@@ -13602,32 +13935,33 @@
           <t>info@helio.se</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>+46 8 522 232 00</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R35" s="5" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S35" s="5" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T35" s="5" t="inlineStr">
+      <c r="U35" s="5" t="inlineStr">
         <is>
           <t>https://helio.se/en/helio-sundbyberg-signalfabriken/</t>
         </is>
       </c>
-      <c r="U35" s="5" t="inlineStr">
+      <c r="V35" s="5" t="inlineStr">
         <is>
           <t>Same chain as Helio Hornstull; one chain-level conversation possible.</t>
         </is>
@@ -13707,32 +14041,33 @@
           <t>maria.ackelman@ahouse.se</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>+46 73 566 26 05</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R36" s="5" t="inlineStr">
+      <c r="S36" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S36" s="5" t="inlineStr">
+      <c r="T36" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T36" s="5" t="inlineStr">
+      <c r="U36" s="5" t="inlineStr">
         <is>
           <t>https://ahouse.se/en/destination/a-house-hagastaden/</t>
         </is>
       </c>
-      <c r="U36" s="5" t="inlineStr">
+      <c r="V36" s="5" t="inlineStr">
         <is>
           <t>A House also in Slussen, Östermalm, Slakthusområdet, Sickla Central. Network of sites could be pitched together.</t>
         </is>
@@ -13808,32 +14143,33 @@
           <t>info@helio.se</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>+46 8 522 232 00</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R37" s="5" t="inlineStr">
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S37" s="5" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T37" s="5" t="inlineStr">
+      <c r="U37" s="5" t="inlineStr">
         <is>
           <t>https://helio.se/en/hornstull/</t>
         </is>
       </c>
-      <c r="U37" s="5" t="inlineStr">
+      <c r="V37" s="5" t="inlineStr">
         <is>
           <t>Several other Stockholm sites (Slussen, Stockholm City, Hotorget, Kungsholmen). Chain-level deal possible.</t>
         </is>
@@ -13897,32 +14233,33 @@
           <t>ark@ahouse.se</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>+46 8 410 899 00</t>
         </is>
       </c>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="R38" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R38" s="5" t="inlineStr">
+      <c r="S38" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S38" s="5" t="inlineStr">
+      <c r="T38" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T38" s="5" t="inlineStr">
+      <c r="U38" s="5" t="inlineStr">
         <is>
           <t>https://ahouse.se/destination/ark/</t>
         </is>
       </c>
-      <c r="U38" s="5" t="inlineStr">
+      <c r="V38" s="5" t="inlineStr">
         <is>
           <t>A House also runs Sickla Central coworking in Nacka; Sting is located here.</t>
         </is>
@@ -13986,32 +14323,33 @@
           <t>stockholm@impacthub.net</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>+46 8-667 49 07</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R39" s="5" t="inlineStr">
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S39" s="5" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T39" s="5" t="inlineStr">
+      <c r="U39" s="5" t="inlineStr">
         <is>
           <t>https://impacthubstockholm.com/</t>
         </is>
       </c>
-      <c r="U39" s="5" t="inlineStr">
+      <c r="V39" s="5" t="inlineStr">
         <is>
           <t>Impact / social entrepreneurship focus. Mailing address Box 7488, 103 92 Stockholm.</t>
         </is>
@@ -14083,32 +14421,33 @@
           <t>info@convendum.se</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>+46 (0)10 510 08 88</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R40" s="5" t="inlineStr">
+      <c r="S40" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S40" s="5" t="inlineStr">
+      <c r="T40" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T40" s="5" t="inlineStr">
+      <c r="U40" s="5" t="inlineStr">
         <is>
           <t>https://convendum.se/en/our-members/</t>
         </is>
       </c>
-      <c r="U40" s="5" t="inlineStr">
+      <c r="V40" s="5" t="inlineStr">
         <is>
           <t>Site managers with personal emails are listed on the members page. Search snippet said about 34 after-work events per year (unverified).</t>
         </is>
@@ -14180,32 +14519,33 @@
           <t>Terese.Alfredeen@fabege.se</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>+46 76 780 80 96</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R41" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S41" s="5" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T41" s="5" t="inlineStr">
+      <c r="U41" s="5" t="inlineStr">
         <is>
           <t>https://www.fabege.se/lediga-lokaler/cow-coworking/cow-hammarby-sjostad/</t>
         </is>
       </c>
-      <c r="U41" s="5" t="inlineStr">
+      <c r="V41" s="5" t="inlineStr">
         <is>
           <t>Weak events evidence. Fabege also runs CoW Hagastaden (Sveavagen 151) and other CoW sites.</t>
         </is>
@@ -14277,39 +14617,40 @@
           <t>sicklacentral@ahouse.se</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>+46 70-083 39 09</t>
         </is>
       </c>
-      <c r="Q42" s="5" t="inlineStr">
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R42" s="5" t="inlineStr">
+      <c r="S42" s="5" t="inlineStr">
         <is>
           <t>Domain or address is on the suppression list (already contacted). Do not contact.</t>
         </is>
       </c>
-      <c r="S42" s="5" t="inlineStr">
+      <c r="T42" s="5" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr">
+      <c r="U42" s="5" t="inlineStr">
         <is>
           <t>https://ahouse.se/destination/sickla-central/</t>
         </is>
       </c>
-      <c r="U42" s="5" t="inlineStr">
+      <c r="V42" s="5" t="inlineStr">
         <is>
           <t>Personal email maria.ackelman@ahouse.se, +46 73 566 26 05 on same page. Nacka. Tenants of the whole tower can join community.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U42"/>
+  <autoFilter ref="A1:V42"/>
   <conditionalFormatting sqref="B2:B42">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B2="A"</formula>
@@ -14328,8 +14669,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="S2:S42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"To do,Contacted,Replied,Call booked,Not interested"</formula1>
+    <dataValidation sqref="T2:T42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Draft ready,To do,Contacted,Sent,Replied,Call booked,Not interested"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
